--- a/ANA/Requisicion_Productos_Torte1_Torte2.xlsx
+++ b/ANA/Requisicion_Productos_Torte1_Torte2.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requisición" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Requisición'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Requisición'!$1:$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,6 +59,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="007B241C"/>
       <sz val="11"/>
     </font>
@@ -78,8 +84,13 @@
       <color rgb="001B2B24"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -108,6 +119,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00A9412F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F6C9B8"/>
       </patternFill>
     </fill>
@@ -122,7 +138,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -154,6 +170,20 @@
       <top style="medium">
         <color rgb="00B0857B"/>
       </top>
+      <bottom style="thin">
+        <color rgb="00D9C3BC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9C3BC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9C3BC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9C3BC"/>
+      </top>
       <bottom style="medium">
         <color rgb="00B0857B"/>
       </bottom>
@@ -162,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -172,43 +202,85 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="001E8449"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D5F5E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <color rgb="007B7B7B"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00EDEDED"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -570,15 +642,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -591,7 +666,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tortas · Control de insumos por sucursal (Torte 1 y Torte 2)</t>
+          <t>Tortas · Control de insumos y compras por sucursal (Torte 1 y Torte 2)</t>
         </is>
       </c>
     </row>
@@ -601,15 +676,17 @@
           <t>Fecha:</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Semana / Turno:</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -617,21 +694,24 @@
           <t>Responsable:</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
+      <c r="B4" s="4" t="n"/>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Instrucciones: anota la CANTIDAD requerida por sucursal en Torte 1 y Torte 2. La columna Total se calcula sola. Ejemplo → Lechuga | pza | Torte 1: 5 | Torte 2: 3 | Total: 8.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Instrucciones: registra la EXISTENCIA (lo que hay) y la cantidad A COMPRAR por sucursal. Total y ¿Comprar? se calculan solos (marca “Sí” si hay algo por comprar). Celdas amarillas = para llenar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Producto</t>
         </is>
@@ -641,966 +721,1330 @@
           <t>Unidad</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>EXISTENCIA / STOCK</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>A COMPRAR</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Total
+a comprar</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>¿Comprar?</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Torte 1</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Torte 2</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Observaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Torte 1</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Torte 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>VERDURAS</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Lechuga</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>pza</t>
-        </is>
-      </c>
+      <c r="B8" s="11" t="n"/>
       <c r="C8" s="11" t="n"/>
       <c r="D8" s="11" t="n"/>
-      <c r="E8" s="12">
-        <f>IF(COUNT(C8:D8)=0,"",SUM(C8:D8))</f>
-        <v/>
-      </c>
-      <c r="F8" s="13" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="11" t="n"/>
+      <c r="I8" s="11" t="n"/>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Lechuga</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>pza</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="15">
+        <f>IF($A9="","",IF(COUNT(E9:F9)=0,"",SUM(E9:F9)))</f>
+        <v/>
+      </c>
+      <c r="H9" s="16">
+        <f>IF($A9="","",IF(SUM(E9:F9)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I9" s="17" t="n"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Aguacate</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="16">
-        <f>IF(COUNT(C9:D9)=0,"",SUM(C9:D9))</f>
-        <v/>
-      </c>
-      <c r="F9" s="17" t="n"/>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="20">
+        <f>IF($A10="","",IF(COUNT(E10:F10)=0,"",SUM(E10:F10)))</f>
+        <v/>
+      </c>
+      <c r="H10" s="21">
+        <f>IF($A10="","",IF(SUM(E10:F10)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I10" s="22" t="n"/>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Jitomate</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="12">
-        <f>IF(COUNT(C10:D10)=0,"",SUM(C10:D10))</f>
-        <v/>
-      </c>
-      <c r="F10" s="13" t="n"/>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="15">
+        <f>IF($A11="","",IF(COUNT(E11:F11)=0,"",SUM(E11:F11)))</f>
+        <v/>
+      </c>
+      <c r="H11" s="16">
+        <f>IF($A11="","",IF(SUM(E11:F11)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I11" s="17" t="n"/>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Cebolla</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="16">
-        <f>IF(COUNT(C11:D11)=0,"",SUM(C11:D11))</f>
-        <v/>
-      </c>
-      <c r="F11" s="17" t="n"/>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="9" t="inlineStr"/>
-      <c r="B12" s="10" t="inlineStr"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="12">
-        <f>IF(COUNT(C12:D12)=0,"",SUM(C12:D12))</f>
-        <v/>
-      </c>
-      <c r="F12" s="13" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="20">
+        <f>IF($A12="","",IF(COUNT(E12:F12)=0,"",SUM(E12:F12)))</f>
+        <v/>
+      </c>
+      <c r="H12" s="21">
+        <f>IF($A12="","",IF(SUM(E12:F12)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I12" s="22" t="n"/>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="14" t="inlineStr"/>
-      <c r="B13" s="15" t="inlineStr"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="16">
-        <f>IF(COUNT(C13:D13)=0,"",SUM(C13:D13))</f>
-        <v/>
-      </c>
-      <c r="F13" s="17" t="n"/>
-    </row>
-    <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="B13" s="13" t="inlineStr"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="15">
+        <f>IF($A13="","",IF(COUNT(E13:F13)=0,"",SUM(E13:F13)))</f>
+        <v/>
+      </c>
+      <c r="H13" s="16">
+        <f>IF($A13="","",IF(SUM(E13:F13)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I13" s="17" t="n"/>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="18" t="inlineStr"/>
+      <c r="B14" s="19" t="inlineStr"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="20">
+        <f>IF($A14="","",IF(COUNT(E14:F14)=0,"",SUM(E14:F14)))</f>
+        <v/>
+      </c>
+      <c r="H14" s="21">
+        <f>IF($A14="","",IF(SUM(E14:F14)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I14" s="22" t="n"/>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>CARNE MART</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Chiles</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>lata</t>
-        </is>
-      </c>
+      <c r="B15" s="11" t="n"/>
       <c r="C15" s="11" t="n"/>
       <c r="D15" s="11" t="n"/>
-      <c r="E15" s="12">
-        <f>IF(COUNT(C15:D15)=0,"",SUM(C15:D15))</f>
-        <v/>
-      </c>
-      <c r="F15" s="13" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Chiles</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>lata</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="15">
+        <f>IF($A16="","",IF(COUNT(E16:F16)=0,"",SUM(E16:F16)))</f>
+        <v/>
+      </c>
+      <c r="H16" s="16">
+        <f>IF($A16="","",IF(SUM(E16:F16)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I16" s="17" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Mayonesa</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="16">
-        <f>IF(COUNT(C16:D16)=0,"",SUM(C16:D16))</f>
-        <v/>
-      </c>
-      <c r="F16" s="17" t="n"/>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="20">
+        <f>IF($A17="","",IF(COUNT(E17:F17)=0,"",SUM(E17:F17)))</f>
+        <v/>
+      </c>
+      <c r="H17" s="21">
+        <f>IF($A17="","",IF(SUM(E17:F17)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I17" s="22" t="n"/>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Mostaza</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="12">
-        <f>IF(COUNT(C17:D17)=0,"",SUM(C17:D17))</f>
-        <v/>
-      </c>
-      <c r="F17" s="13" t="n"/>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="15">
+        <f>IF($A18="","",IF(COUNT(E18:F18)=0,"",SUM(E18:F18)))</f>
+        <v/>
+      </c>
+      <c r="H18" s="16">
+        <f>IF($A18="","",IF(SUM(E18:F18)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I18" s="17" t="n"/>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Manteca</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="16">
-        <f>IF(COUNT(C18:D18)=0,"",SUM(C18:D18))</f>
-        <v/>
-      </c>
-      <c r="F18" s="17" t="n"/>
-    </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="9" t="inlineStr"/>
-      <c r="B19" s="10" t="inlineStr"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="12">
-        <f>IF(COUNT(C19:D19)=0,"",SUM(C19:D19))</f>
-        <v/>
-      </c>
-      <c r="F19" s="13" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="20">
+        <f>IF($A19="","",IF(COUNT(E19:F19)=0,"",SUM(E19:F19)))</f>
+        <v/>
+      </c>
+      <c r="H19" s="21">
+        <f>IF($A19="","",IF(SUM(E19:F19)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I19" s="22" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="14" t="inlineStr"/>
-      <c r="B20" s="15" t="inlineStr"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="16">
-        <f>IF(COUNT(C20:D20)=0,"",SUM(C20:D20))</f>
-        <v/>
-      </c>
-      <c r="F20" s="17" t="n"/>
-    </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr"/>
+      <c r="B20" s="13" t="inlineStr"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="15">
+        <f>IF($A20="","",IF(COUNT(E20:F20)=0,"",SUM(E20:F20)))</f>
+        <v/>
+      </c>
+      <c r="H20" s="16">
+        <f>IF($A20="","",IF(SUM(E20:F20)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I20" s="17" t="n"/>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="18" t="inlineStr"/>
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="20">
+        <f>IF($A21="","",IF(COUNT(E21:F21)=0,"",SUM(E21:F21)))</f>
+        <v/>
+      </c>
+      <c r="H21" s="21">
+        <f>IF($A21="","",IF(SUM(E21:F21)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I21" s="22" t="n"/>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>CÁRNICOS / POA</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>Bistec / Adobada</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+      <c r="B22" s="11" t="n"/>
       <c r="C22" s="11" t="n"/>
       <c r="D22" s="11" t="n"/>
-      <c r="E22" s="12">
-        <f>IF(COUNT(C22:D22)=0,"",SUM(C22:D22))</f>
-        <v/>
-      </c>
-      <c r="F22" s="13" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="11" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="11" t="n"/>
+      <c r="I22" s="11" t="n"/>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Bistec / Adobada</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="15">
+        <f>IF($A23="","",IF(COUNT(E23:F23)=0,"",SUM(E23:F23)))</f>
+        <v/>
+      </c>
+      <c r="H23" s="16">
+        <f>IF($A23="","",IF(SUM(E23:F23)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I23" s="17" t="n"/>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>Pierna</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="16">
-        <f>IF(COUNT(C23:D23)=0,"",SUM(C23:D23))</f>
-        <v/>
-      </c>
-      <c r="F23" s="17" t="n"/>
-    </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="20">
+        <f>IF($A24="","",IF(COUNT(E24:F24)=0,"",SUM(E24:F24)))</f>
+        <v/>
+      </c>
+      <c r="H24" s="21">
+        <f>IF($A24="","",IF(SUM(E24:F24)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I24" s="22" t="n"/>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Chorizo</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="12">
-        <f>IF(COUNT(C24:D24)=0,"",SUM(C24:D24))</f>
-        <v/>
-      </c>
-      <c r="F24" s="13" t="n"/>
-    </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="15">
+        <f>IF($A25="","",IF(COUNT(E25:F25)=0,"",SUM(E25:F25)))</f>
+        <v/>
+      </c>
+      <c r="H25" s="16">
+        <f>IF($A25="","",IF(SUM(E25:F25)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I25" s="17" t="n"/>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>Jamón</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="16">
-        <f>IF(COUNT(C25:D25)=0,"",SUM(C25:D25))</f>
-        <v/>
-      </c>
-      <c r="F25" s="17" t="n"/>
-    </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="20">
+        <f>IF($A26="","",IF(COUNT(E26:F26)=0,"",SUM(E26:F26)))</f>
+        <v/>
+      </c>
+      <c r="H26" s="21">
+        <f>IF($A26="","",IF(SUM(E26:F26)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Huevo</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="12">
-        <f>IF(COUNT(C26:D26)=0,"",SUM(C26:D26))</f>
-        <v/>
-      </c>
-      <c r="F26" s="13" t="n"/>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="14" t="n"/>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="15">
+        <f>IF($A27="","",IF(COUNT(E27:F27)=0,"",SUM(E27:F27)))</f>
+        <v/>
+      </c>
+      <c r="H27" s="16">
+        <f>IF($A27="","",IF(SUM(E27:F27)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I27" s="17" t="n"/>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>Queso</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="16">
-        <f>IF(COUNT(C27:D27)=0,"",SUM(C27:D27))</f>
-        <v/>
-      </c>
-      <c r="F27" s="17" t="n"/>
-    </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="20">
+        <f>IF($A28="","",IF(COUNT(E28:F28)=0,"",SUM(E28:F28)))</f>
+        <v/>
+      </c>
+      <c r="H28" s="21">
+        <f>IF($A28="","",IF(SUM(E28:F28)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>Leche</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>lt</t>
         </is>
       </c>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="12">
-        <f>IF(COUNT(C28:D28)=0,"",SUM(C28:D28))</f>
-        <v/>
-      </c>
-      <c r="F28" s="13" t="n"/>
-    </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="14" t="inlineStr"/>
-      <c r="B29" s="15" t="inlineStr"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="16">
-        <f>IF(COUNT(C29:D29)=0,"",SUM(C29:D29))</f>
-        <v/>
-      </c>
-      <c r="F29" s="17" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="15">
+        <f>IF($A29="","",IF(COUNT(E29:F29)=0,"",SUM(E29:F29)))</f>
+        <v/>
+      </c>
+      <c r="H29" s="16">
+        <f>IF($A29="","",IF(SUM(E29:F29)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I29" s="17" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="9" t="inlineStr"/>
-      <c r="B30" s="10" t="inlineStr"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="12">
-        <f>IF(COUNT(C30:D30)=0,"",SUM(C30:D30))</f>
-        <v/>
-      </c>
-      <c r="F30" s="13" t="n"/>
-    </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A30" s="18" t="inlineStr"/>
+      <c r="B30" s="19" t="inlineStr"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="20">
+        <f>IF($A30="","",IF(COUNT(E30:F30)=0,"",SUM(E30:F30)))</f>
+        <v/>
+      </c>
+      <c r="H30" s="21">
+        <f>IF($A30="","",IF(SUM(E30:F30)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="12" t="inlineStr"/>
+      <c r="B31" s="13" t="inlineStr"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="15">
+        <f>IF($A31="","",IF(COUNT(E31:F31)=0,"",SUM(E31:F31)))</f>
+        <v/>
+      </c>
+      <c r="H31" s="16">
+        <f>IF($A31="","",IF(SUM(E31:F31)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I31" s="17" t="n"/>
+    </row>
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>CONDIMENTOS</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-    </row>
-    <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>Pimienta</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>pza</t>
-        </is>
-      </c>
+      <c r="B32" s="11" t="n"/>
       <c r="C32" s="11" t="n"/>
       <c r="D32" s="11" t="n"/>
-      <c r="E32" s="12">
-        <f>IF(COUNT(C32:D32)=0,"",SUM(C32:D32))</f>
-        <v/>
-      </c>
-      <c r="F32" s="13" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="11" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="11" t="n"/>
+      <c r="I32" s="11" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Pimienta</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>pza</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="14" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="15">
+        <f>IF($A33="","",IF(COUNT(E33:F33)=0,"",SUM(E33:F33)))</f>
+        <v/>
+      </c>
+      <c r="H33" s="16">
+        <f>IF($A33="","",IF(SUM(E33:F33)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I33" s="17" t="n"/>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>Ajo en polvo</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="16">
-        <f>IF(COUNT(C33:D33)=0,"",SUM(C33:D33))</f>
-        <v/>
-      </c>
-      <c r="F33" s="17" t="n"/>
-    </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="14" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="20">
+        <f>IF($A34="","",IF(COUNT(E34:F34)=0,"",SUM(E34:F34)))</f>
+        <v/>
+      </c>
+      <c r="H34" s="21">
+        <f>IF($A34="","",IF(SUM(E34:F34)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I34" s="22" t="n"/>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>Sazonador</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="12">
-        <f>IF(COUNT(C34:D34)=0,"",SUM(C34:D34))</f>
-        <v/>
-      </c>
-      <c r="F34" s="13" t="n"/>
-    </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="15">
+        <f>IF($A35="","",IF(COUNT(E35:F35)=0,"",SUM(E35:F35)))</f>
+        <v/>
+      </c>
+      <c r="H35" s="16">
+        <f>IF($A35="","",IF(SUM(E35:F35)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I35" s="17" t="n"/>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>Salsa Inglesa</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="16">
-        <f>IF(COUNT(C35:D35)=0,"",SUM(C35:D35))</f>
-        <v/>
-      </c>
-      <c r="F35" s="17" t="n"/>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="20">
+        <f>IF($A36="","",IF(COUNT(E36:F36)=0,"",SUM(E36:F36)))</f>
+        <v/>
+      </c>
+      <c r="H36" s="21">
+        <f>IF($A36="","",IF(SUM(E36:F36)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I36" s="22" t="n"/>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>Jugo Maggi</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="12">
-        <f>IF(COUNT(C36:D36)=0,"",SUM(C36:D36))</f>
-        <v/>
-      </c>
-      <c r="F36" s="13" t="n"/>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="15">
+        <f>IF($A37="","",IF(COUNT(E37:F37)=0,"",SUM(E37:F37)))</f>
+        <v/>
+      </c>
+      <c r="H37" s="16">
+        <f>IF($A37="","",IF(SUM(E37:F37)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I37" s="17" t="n"/>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>Aceite</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t>lt</t>
         </is>
       </c>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="16">
-        <f>IF(COUNT(C37:D37)=0,"",SUM(C37:D37))</f>
-        <v/>
-      </c>
-      <c r="F37" s="17" t="n"/>
-    </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="9" t="inlineStr"/>
-      <c r="B38" s="10" t="inlineStr"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="12">
-        <f>IF(COUNT(C38:D38)=0,"",SUM(C38:D38))</f>
-        <v/>
-      </c>
-      <c r="F38" s="13" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="14" t="n"/>
+      <c r="F38" s="14" t="n"/>
+      <c r="G38" s="20">
+        <f>IF($A38="","",IF(COUNT(E38:F38)=0,"",SUM(E38:F38)))</f>
+        <v/>
+      </c>
+      <c r="H38" s="21">
+        <f>IF($A38="","",IF(SUM(E38:F38)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I38" s="22" t="n"/>
     </row>
     <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="14" t="inlineStr"/>
-      <c r="B39" s="15" t="inlineStr"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="16">
-        <f>IF(COUNT(C39:D39)=0,"",SUM(C39:D39))</f>
-        <v/>
-      </c>
-      <c r="F39" s="17" t="n"/>
-    </row>
-    <row r="40" ht="19" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A39" s="12" t="inlineStr"/>
+      <c r="B39" s="13" t="inlineStr"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="14" t="n"/>
+      <c r="G39" s="15">
+        <f>IF($A39="","",IF(COUNT(E39:F39)=0,"",SUM(E39:F39)))</f>
+        <v/>
+      </c>
+      <c r="H39" s="16">
+        <f>IF($A39="","",IF(SUM(E39:F39)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I39" s="17" t="n"/>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="18" t="inlineStr"/>
+      <c r="B40" s="19" t="inlineStr"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="14" t="n"/>
+      <c r="E40" s="14" t="n"/>
+      <c r="F40" s="14" t="n"/>
+      <c r="G40" s="20">
+        <f>IF($A40="","",IF(COUNT(E40:F40)=0,"",SUM(E40:F40)))</f>
+        <v/>
+      </c>
+      <c r="H40" s="21">
+        <f>IF($A40="","",IF(SUM(E40:F40)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="19" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>LIMPIEZA</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-    </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>Cloro</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>lt</t>
-        </is>
-      </c>
+      <c r="B41" s="11" t="n"/>
       <c r="C41" s="11" t="n"/>
       <c r="D41" s="11" t="n"/>
-      <c r="E41" s="12">
-        <f>IF(COUNT(C41:D41)=0,"",SUM(C41:D41))</f>
-        <v/>
-      </c>
-      <c r="F41" s="13" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="11" t="n"/>
+      <c r="G41" s="11" t="n"/>
+      <c r="H41" s="11" t="n"/>
+      <c r="I41" s="11" t="n"/>
     </row>
     <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="14" t="inlineStr">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Cloro</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>lt</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="14" t="n"/>
+      <c r="E42" s="14" t="n"/>
+      <c r="F42" s="14" t="n"/>
+      <c r="G42" s="15">
+        <f>IF($A42="","",IF(COUNT(E42:F42)=0,"",SUM(E42:F42)))</f>
+        <v/>
+      </c>
+      <c r="H42" s="16">
+        <f>IF($A42="","",IF(SUM(E42:F42)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I42" s="17" t="n"/>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>Fabuloso</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B43" s="19" t="inlineStr">
         <is>
           <t>lt</t>
         </is>
       </c>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="16">
-        <f>IF(COUNT(C42:D42)=0,"",SUM(C42:D42))</f>
-        <v/>
-      </c>
-      <c r="F42" s="17" t="n"/>
-    </row>
-    <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="C43" s="14" t="n"/>
+      <c r="D43" s="14" t="n"/>
+      <c r="E43" s="14" t="n"/>
+      <c r="F43" s="14" t="n"/>
+      <c r="G43" s="20">
+        <f>IF($A43="","",IF(COUNT(E43:F43)=0,"",SUM(E43:F43)))</f>
+        <v/>
+      </c>
+      <c r="H43" s="21">
+        <f>IF($A43="","",IF(SUM(E43:F43)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>Desengrasante</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>lt</t>
         </is>
       </c>
-      <c r="C43" s="11" t="n"/>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="12">
-        <f>IF(COUNT(C43:D43)=0,"",SUM(C43:D43))</f>
-        <v/>
-      </c>
-      <c r="F43" s="13" t="n"/>
-    </row>
-    <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="14" t="inlineStr"/>
-      <c r="B44" s="15" t="inlineStr"/>
-      <c r="C44" s="11" t="n"/>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="16">
-        <f>IF(COUNT(C44:D44)=0,"",SUM(C44:D44))</f>
-        <v/>
-      </c>
-      <c r="F44" s="17" t="n"/>
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="14" t="n"/>
+      <c r="E44" s="14" t="n"/>
+      <c r="F44" s="14" t="n"/>
+      <c r="G44" s="15">
+        <f>IF($A44="","",IF(COUNT(E44:F44)=0,"",SUM(E44:F44)))</f>
+        <v/>
+      </c>
+      <c r="H44" s="16">
+        <f>IF($A44="","",IF(SUM(E44:F44)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I44" s="17" t="n"/>
     </row>
     <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="9" t="inlineStr"/>
-      <c r="B45" s="10" t="inlineStr"/>
-      <c r="C45" s="11" t="n"/>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="12">
-        <f>IF(COUNT(C45:D45)=0,"",SUM(C45:D45))</f>
-        <v/>
-      </c>
-      <c r="F45" s="13" t="n"/>
-    </row>
-    <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A45" s="18" t="inlineStr"/>
+      <c r="B45" s="19" t="inlineStr"/>
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="14" t="n"/>
+      <c r="E45" s="14" t="n"/>
+      <c r="F45" s="14" t="n"/>
+      <c r="G45" s="20">
+        <f>IF($A45="","",IF(COUNT(E45:F45)=0,"",SUM(E45:F45)))</f>
+        <v/>
+      </c>
+      <c r="H45" s="21">
+        <f>IF($A45="","",IF(SUM(E45:F45)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I45" s="22" t="n"/>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="12" t="inlineStr"/>
+      <c r="B46" s="13" t="inlineStr"/>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="14" t="n"/>
+      <c r="E46" s="14" t="n"/>
+      <c r="F46" s="14" t="n"/>
+      <c r="G46" s="15">
+        <f>IF($A46="","",IF(COUNT(E46:F46)=0,"",SUM(E46:F46)))</f>
+        <v/>
+      </c>
+      <c r="H46" s="16">
+        <f>IF($A46="","",IF(SUM(E46:F46)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I46" s="17" t="n"/>
+    </row>
+    <row r="47" ht="19" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>PAPELERÍA</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n"/>
-      <c r="C46" s="5" t="n"/>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="n"/>
-    </row>
-    <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="9" t="inlineStr">
-        <is>
-          <t>Servilletas</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t>paq</t>
-        </is>
-      </c>
+      <c r="B47" s="11" t="n"/>
       <c r="C47" s="11" t="n"/>
       <c r="D47" s="11" t="n"/>
-      <c r="E47" s="12">
-        <f>IF(COUNT(C47:D47)=0,"",SUM(C47:D47))</f>
-        <v/>
-      </c>
-      <c r="F47" s="13" t="n"/>
+      <c r="E47" s="11" t="n"/>
+      <c r="F47" s="11" t="n"/>
+      <c r="G47" s="11" t="n"/>
+      <c r="H47" s="11" t="n"/>
+      <c r="I47" s="11" t="n"/>
     </row>
     <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="14" t="inlineStr">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Servilletas</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>paq</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="14" t="n"/>
+      <c r="E48" s="14" t="n"/>
+      <c r="F48" s="14" t="n"/>
+      <c r="G48" s="15">
+        <f>IF($A48="","",IF(COUNT(E48:F48)=0,"",SUM(E48:F48)))</f>
+        <v/>
+      </c>
+      <c r="H48" s="16">
+        <f>IF($A48="","",IF(SUM(E48:F48)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I48" s="17" t="n"/>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>Sanitas</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t>paq</t>
         </is>
       </c>
-      <c r="C48" s="11" t="n"/>
-      <c r="D48" s="11" t="n"/>
-      <c r="E48" s="16">
-        <f>IF(COUNT(C48:D48)=0,"",SUM(C48:D48))</f>
-        <v/>
-      </c>
-      <c r="F48" s="17" t="n"/>
-    </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="14" t="n"/>
+      <c r="E49" s="14" t="n"/>
+      <c r="F49" s="14" t="n"/>
+      <c r="G49" s="20">
+        <f>IF($A49="","",IF(COUNT(E49:F49)=0,"",SUM(E49:F49)))</f>
+        <v/>
+      </c>
+      <c r="H49" s="21">
+        <f>IF($A49="","",IF(SUM(E49:F49)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I49" s="22" t="n"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>Aluminio</t>
         </is>
       </c>
-      <c r="B49" s="10" t="inlineStr">
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>rollo</t>
         </is>
       </c>
-      <c r="C49" s="11" t="n"/>
-      <c r="D49" s="11" t="n"/>
-      <c r="E49" s="12">
-        <f>IF(COUNT(C49:D49)=0,"",SUM(C49:D49))</f>
-        <v/>
-      </c>
-      <c r="F49" s="13" t="n"/>
-    </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="14" t="inlineStr">
+      <c r="C50" s="14" t="n"/>
+      <c r="D50" s="14" t="n"/>
+      <c r="E50" s="14" t="n"/>
+      <c r="F50" s="14" t="n"/>
+      <c r="G50" s="15">
+        <f>IF($A50="","",IF(COUNT(E50:F50)=0,"",SUM(E50:F50)))</f>
+        <v/>
+      </c>
+      <c r="H50" s="16">
+        <f>IF($A50="","",IF(SUM(E50:F50)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I50" s="17" t="n"/>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="18" t="inlineStr">
         <is>
           <t>Papel de baño</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B51" s="19" t="inlineStr">
         <is>
           <t>paq</t>
         </is>
       </c>
-      <c r="C50" s="11" t="n"/>
-      <c r="D50" s="11" t="n"/>
-      <c r="E50" s="16">
-        <f>IF(COUNT(C50:D50)=0,"",SUM(C50:D50))</f>
-        <v/>
-      </c>
-      <c r="F50" s="17" t="n"/>
-    </row>
-    <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="C51" s="14" t="n"/>
+      <c r="D51" s="14" t="n"/>
+      <c r="E51" s="14" t="n"/>
+      <c r="F51" s="14" t="n"/>
+      <c r="G51" s="20">
+        <f>IF($A51="","",IF(COUNT(E51:F51)=0,"",SUM(E51:F51)))</f>
+        <v/>
+      </c>
+      <c r="H51" s="21">
+        <f>IF($A51="","",IF(SUM(E51:F51)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I51" s="22" t="n"/>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t>Servitoalla</t>
         </is>
       </c>
-      <c r="B51" s="10" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>paq</t>
         </is>
       </c>
-      <c r="C51" s="11" t="n"/>
-      <c r="D51" s="11" t="n"/>
-      <c r="E51" s="12">
-        <f>IF(COUNT(C51:D51)=0,"",SUM(C51:D51))</f>
-        <v/>
-      </c>
-      <c r="F51" s="13" t="n"/>
-    </row>
-    <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="14" t="inlineStr"/>
-      <c r="B52" s="15" t="inlineStr"/>
-      <c r="C52" s="11" t="n"/>
-      <c r="D52" s="11" t="n"/>
-      <c r="E52" s="16">
-        <f>IF(COUNT(C52:D52)=0,"",SUM(C52:D52))</f>
-        <v/>
-      </c>
-      <c r="F52" s="17" t="n"/>
+      <c r="C52" s="14" t="n"/>
+      <c r="D52" s="14" t="n"/>
+      <c r="E52" s="14" t="n"/>
+      <c r="F52" s="14" t="n"/>
+      <c r="G52" s="15">
+        <f>IF($A52="","",IF(COUNT(E52:F52)=0,"",SUM(E52:F52)))</f>
+        <v/>
+      </c>
+      <c r="H52" s="16">
+        <f>IF($A52="","",IF(SUM(E52:F52)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I52" s="17" t="n"/>
     </row>
     <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="9" t="inlineStr"/>
-      <c r="B53" s="10" t="inlineStr"/>
-      <c r="C53" s="11" t="n"/>
-      <c r="D53" s="11" t="n"/>
-      <c r="E53" s="12">
-        <f>IF(COUNT(C53:D53)=0,"",SUM(C53:D53))</f>
-        <v/>
-      </c>
-      <c r="F53" s="13" t="n"/>
-    </row>
-    <row r="54" ht="19" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A53" s="18" t="inlineStr"/>
+      <c r="B53" s="19" t="inlineStr"/>
+      <c r="C53" s="14" t="n"/>
+      <c r="D53" s="14" t="n"/>
+      <c r="E53" s="14" t="n"/>
+      <c r="F53" s="14" t="n"/>
+      <c r="G53" s="20">
+        <f>IF($A53="","",IF(COUNT(E53:F53)=0,"",SUM(E53:F53)))</f>
+        <v/>
+      </c>
+      <c r="H53" s="21">
+        <f>IF($A53="","",IF(SUM(E53:F53)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I53" s="22" t="n"/>
+    </row>
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="12" t="inlineStr"/>
+      <c r="B54" s="13" t="inlineStr"/>
+      <c r="C54" s="14" t="n"/>
+      <c r="D54" s="14" t="n"/>
+      <c r="E54" s="14" t="n"/>
+      <c r="F54" s="14" t="n"/>
+      <c r="G54" s="15">
+        <f>IF($A54="","",IF(COUNT(E54:F54)=0,"",SUM(E54:F54)))</f>
+        <v/>
+      </c>
+      <c r="H54" s="16">
+        <f>IF($A54="","",IF(SUM(E54:F54)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I54" s="17" t="n"/>
+    </row>
+    <row r="55" ht="19" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>OTROS</t>
         </is>
       </c>
-      <c r="B54" s="5" t="n"/>
-      <c r="C54" s="5" t="n"/>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="n"/>
-    </row>
-    <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>Tortillas</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+      <c r="B55" s="11" t="n"/>
       <c r="C55" s="11" t="n"/>
       <c r="D55" s="11" t="n"/>
-      <c r="E55" s="12">
-        <f>IF(COUNT(C55:D55)=0,"",SUM(C55:D55))</f>
-        <v/>
-      </c>
-      <c r="F55" s="13" t="n"/>
+      <c r="E55" s="11" t="n"/>
+      <c r="F55" s="11" t="n"/>
+      <c r="G55" s="11" t="n"/>
+      <c r="H55" s="11" t="n"/>
+      <c r="I55" s="11" t="n"/>
     </row>
     <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="14" t="inlineStr">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>Tortillas</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="n"/>
+      <c r="D56" s="14" t="n"/>
+      <c r="E56" s="14" t="n"/>
+      <c r="F56" s="14" t="n"/>
+      <c r="G56" s="15">
+        <f>IF($A56="","",IF(COUNT(E56:F56)=0,"",SUM(E56:F56)))</f>
+        <v/>
+      </c>
+      <c r="H56" s="16">
+        <f>IF($A56="","",IF(SUM(E56:F56)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I56" s="17" t="n"/>
+    </row>
+    <row r="57" ht="17" customHeight="1">
+      <c r="A57" s="18" t="inlineStr">
         <is>
           <t>Porcionadoras</t>
         </is>
       </c>
-      <c r="B56" s="15" t="inlineStr">
+      <c r="B57" s="19" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C56" s="11" t="n"/>
-      <c r="D56" s="11" t="n"/>
-      <c r="E56" s="16">
-        <f>IF(COUNT(C56:D56)=0,"",SUM(C56:D56))</f>
-        <v/>
-      </c>
-      <c r="F56" s="17" t="n"/>
-    </row>
-    <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="C57" s="14" t="n"/>
+      <c r="D57" s="14" t="n"/>
+      <c r="E57" s="14" t="n"/>
+      <c r="F57" s="14" t="n"/>
+      <c r="G57" s="20">
+        <f>IF($A57="","",IF(COUNT(E57:F57)=0,"",SUM(E57:F57)))</f>
+        <v/>
+      </c>
+      <c r="H57" s="21">
+        <f>IF($A57="","",IF(SUM(E57:F57)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I57" s="22" t="n"/>
+    </row>
+    <row r="58" ht="17" customHeight="1">
+      <c r="A58" s="12" t="inlineStr">
         <is>
           <t>Bolsas para basura</t>
         </is>
       </c>
-      <c r="B57" s="10" t="inlineStr">
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>paq</t>
         </is>
       </c>
-      <c r="C57" s="11" t="n"/>
-      <c r="D57" s="11" t="n"/>
-      <c r="E57" s="12">
-        <f>IF(COUNT(C57:D57)=0,"",SUM(C57:D57))</f>
-        <v/>
-      </c>
-      <c r="F57" s="13" t="n"/>
-    </row>
-    <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="14" t="inlineStr">
+      <c r="C58" s="14" t="n"/>
+      <c r="D58" s="14" t="n"/>
+      <c r="E58" s="14" t="n"/>
+      <c r="F58" s="14" t="n"/>
+      <c r="G58" s="15">
+        <f>IF($A58="","",IF(COUNT(E58:F58)=0,"",SUM(E58:F58)))</f>
+        <v/>
+      </c>
+      <c r="H58" s="16">
+        <f>IF($A58="","",IF(SUM(E58:F58)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I58" s="17" t="n"/>
+    </row>
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" s="18" t="inlineStr">
         <is>
           <t>Microdyn</t>
         </is>
       </c>
-      <c r="B58" s="15" t="inlineStr">
+      <c r="B59" s="19" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C58" s="11" t="n"/>
-      <c r="D58" s="11" t="n"/>
-      <c r="E58" s="16">
-        <f>IF(COUNT(C58:D58)=0,"",SUM(C58:D58))</f>
-        <v/>
-      </c>
-      <c r="F58" s="17" t="n"/>
-    </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="C59" s="14" t="n"/>
+      <c r="D59" s="14" t="n"/>
+      <c r="E59" s="14" t="n"/>
+      <c r="F59" s="14" t="n"/>
+      <c r="G59" s="20">
+        <f>IF($A59="","",IF(COUNT(E59:F59)=0,"",SUM(E59:F59)))</f>
+        <v/>
+      </c>
+      <c r="H59" s="21">
+        <f>IF($A59="","",IF(SUM(E59:F59)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I59" s="22" t="n"/>
+    </row>
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="12" t="inlineStr">
         <is>
           <t>Malteada chocolate</t>
         </is>
       </c>
-      <c r="B59" s="10" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C59" s="11" t="n"/>
-      <c r="D59" s="11" t="n"/>
-      <c r="E59" s="12">
-        <f>IF(COUNT(C59:D59)=0,"",SUM(C59:D59))</f>
-        <v/>
-      </c>
-      <c r="F59" s="13" t="n"/>
-    </row>
-    <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="14" t="inlineStr">
+      <c r="C60" s="14" t="n"/>
+      <c r="D60" s="14" t="n"/>
+      <c r="E60" s="14" t="n"/>
+      <c r="F60" s="14" t="n"/>
+      <c r="G60" s="15">
+        <f>IF($A60="","",IF(COUNT(E60:F60)=0,"",SUM(E60:F60)))</f>
+        <v/>
+      </c>
+      <c r="H60" s="16">
+        <f>IF($A60="","",IF(SUM(E60:F60)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I60" s="17" t="n"/>
+    </row>
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="18" t="inlineStr">
         <is>
           <t>Malteada fresa</t>
         </is>
       </c>
-      <c r="B60" s="15" t="inlineStr">
+      <c r="B61" s="19" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C60" s="11" t="n"/>
-      <c r="D60" s="11" t="n"/>
-      <c r="E60" s="16">
-        <f>IF(COUNT(C60:D60)=0,"",SUM(C60:D60))</f>
-        <v/>
-      </c>
-      <c r="F60" s="17" t="n"/>
-    </row>
-    <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="C61" s="14" t="n"/>
+      <c r="D61" s="14" t="n"/>
+      <c r="E61" s="14" t="n"/>
+      <c r="F61" s="14" t="n"/>
+      <c r="G61" s="20">
+        <f>IF($A61="","",IF(COUNT(E61:F61)=0,"",SUM(E61:F61)))</f>
+        <v/>
+      </c>
+      <c r="H61" s="21">
+        <f>IF($A61="","",IF(SUM(E61:F61)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I61" s="22" t="n"/>
+    </row>
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>Malteada vainilla</t>
         </is>
       </c>
-      <c r="B61" s="10" t="inlineStr">
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C61" s="11" t="n"/>
-      <c r="D61" s="11" t="n"/>
-      <c r="E61" s="12">
-        <f>IF(COUNT(C61:D61)=0,"",SUM(C61:D61))</f>
-        <v/>
-      </c>
-      <c r="F61" s="13" t="n"/>
-    </row>
-    <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="14" t="inlineStr"/>
-      <c r="B62" s="15" t="inlineStr"/>
-      <c r="C62" s="11" t="n"/>
-      <c r="D62" s="11" t="n"/>
-      <c r="E62" s="16">
-        <f>IF(COUNT(C62:D62)=0,"",SUM(C62:D62))</f>
-        <v/>
-      </c>
-      <c r="F62" s="17" t="n"/>
+      <c r="C62" s="14" t="n"/>
+      <c r="D62" s="14" t="n"/>
+      <c r="E62" s="14" t="n"/>
+      <c r="F62" s="14" t="n"/>
+      <c r="G62" s="15">
+        <f>IF($A62="","",IF(COUNT(E62:F62)=0,"",SUM(E62:F62)))</f>
+        <v/>
+      </c>
+      <c r="H62" s="16">
+        <f>IF($A62="","",IF(SUM(E62:F62)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I62" s="17" t="n"/>
     </row>
     <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="9" t="inlineStr"/>
-      <c r="B63" s="10" t="inlineStr"/>
-      <c r="C63" s="11" t="n"/>
-      <c r="D63" s="11" t="n"/>
-      <c r="E63" s="12">
-        <f>IF(COUNT(C63:D63)=0,"",SUM(C63:D63))</f>
-        <v/>
-      </c>
-      <c r="F63" s="13" t="n"/>
+      <c r="A63" s="18" t="inlineStr"/>
+      <c r="B63" s="19" t="inlineStr"/>
+      <c r="C63" s="14" t="n"/>
+      <c r="D63" s="14" t="n"/>
+      <c r="E63" s="14" t="n"/>
+      <c r="F63" s="14" t="n"/>
+      <c r="G63" s="20">
+        <f>IF($A63="","",IF(COUNT(E63:F63)=0,"",SUM(E63:F63)))</f>
+        <v/>
+      </c>
+      <c r="H63" s="21">
+        <f>IF($A63="","",IF(SUM(E63:F63)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I63" s="22" t="n"/>
+    </row>
+    <row r="64" ht="17" customHeight="1">
+      <c r="A64" s="12" t="inlineStr"/>
+      <c r="B64" s="13" t="inlineStr"/>
+      <c r="C64" s="14" t="n"/>
+      <c r="D64" s="14" t="n"/>
+      <c r="E64" s="14" t="n"/>
+      <c r="F64" s="14" t="n"/>
+      <c r="G64" s="15">
+        <f>IF($A64="","",IF(COUNT(E64:F64)=0,"",SUM(E64:F64)))</f>
+        <v/>
+      </c>
+      <c r="H64" s="16">
+        <f>IF($A64="","",IF(SUM(E64:F64)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I64" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="F3"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A7:F7"/>
+  <mergeCells count="20">
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="B4:I4"/>
   </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <conditionalFormatting sqref="H8:H64">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$H8="Sí"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>$H8="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/ANA/Requisicion_Productos_Torte1_Torte2.xlsx
+++ b/ANA/Requisicion_Productos_Torte1_Torte2.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requisición" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Requisición'!$1:$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Requisición'!$1:$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,14 +30,21 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <i val="1"/>
+      <color rgb="009C2A1B"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="18"/>
+      <sz val="17"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10.5"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -99,6 +106,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="009C2A1B"/>
       </patternFill>
     </fill>
@@ -125,11 +137,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F6C9B8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -192,61 +199,64 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -351,6 +361,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1381125" cy="628650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -642,7 +682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -656,1395 +696,1404 @@
     <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="58" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sucursales:  Torte 1  ·  Torte 2      </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
           <t>REQUISICIÓN DE PRODUCTOS</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Tortas · Control de insumos y compras por sucursal (Torte 1 y Torte 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>Control de insumos y compras por sucursal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>Fecha:</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Semana / Turno:</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Responsable:</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Instrucciones: registra la EXISTENCIA (lo que hay) y la cantidad A COMPRAR por sucursal. Total y ¿Comprar? se calculan solos (marca “Sí” si hay algo por comprar). Celdas amarillas = para llenar.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>EXISTENCIA / STOCK</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>A COMPRAR</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Total
 a comprar</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>¿Comprar?</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="C7" s="9" t="inlineStr">
+    <row r="8" ht="16" customHeight="1">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Torte 1</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Torte 2</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Torte 1</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Torte 2</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="19" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>VERDURAS</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="11" t="n"/>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Lechuga</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15">
-        <f>IF($A9="","",IF(COUNT(E9:F9)=0,"",SUM(E9:F9)))</f>
-        <v/>
-      </c>
-      <c r="H9" s="16">
-        <f>IF($A9="","",IF(SUM(E9:F9)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I9" s="17" t="n"/>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="16">
+        <f>IF($A10="","",IF(COUNT(E10:F10)=0,"",SUM(E10:F10)))</f>
+        <v/>
+      </c>
+      <c r="H10" s="17">
+        <f>IF($A10="","",IF(SUM(E10:F10)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I10" s="18" t="n"/>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Aguacate</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="20">
-        <f>IF($A10="","",IF(COUNT(E10:F10)=0,"",SUM(E10:F10)))</f>
-        <v/>
-      </c>
-      <c r="H10" s="21">
-        <f>IF($A10="","",IF(SUM(E10:F10)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I10" s="22" t="n"/>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="21">
+        <f>IF($A11="","",IF(COUNT(E11:F11)=0,"",SUM(E11:F11)))</f>
+        <v/>
+      </c>
+      <c r="H11" s="22">
+        <f>IF($A11="","",IF(SUM(E11:F11)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I11" s="23" t="n"/>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Jitomate</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="15">
-        <f>IF($A11="","",IF(COUNT(E11:F11)=0,"",SUM(E11:F11)))</f>
-        <v/>
-      </c>
-      <c r="H11" s="16">
-        <f>IF($A11="","",IF(SUM(E11:F11)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I11" s="17" t="n"/>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="16">
+        <f>IF($A12="","",IF(COUNT(E12:F12)=0,"",SUM(E12:F12)))</f>
+        <v/>
+      </c>
+      <c r="H12" s="17">
+        <f>IF($A12="","",IF(SUM(E12:F12)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I12" s="18" t="n"/>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Cebolla</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="20">
-        <f>IF($A12="","",IF(COUNT(E12:F12)=0,"",SUM(E12:F12)))</f>
-        <v/>
-      </c>
-      <c r="H12" s="21">
-        <f>IF($A12="","",IF(SUM(E12:F12)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I12" s="22" t="n"/>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="12" t="inlineStr"/>
-      <c r="B13" s="13" t="inlineStr"/>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="14" t="n"/>
-      <c r="E13" s="14" t="n"/>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15">
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="21">
         <f>IF($A13="","",IF(COUNT(E13:F13)=0,"",SUM(E13:F13)))</f>
         <v/>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="22">
         <f>IF($A13="","",IF(SUM(E13:F13)&gt;0,"Sí","No"))</f>
         <v/>
       </c>
-      <c r="I13" s="17" t="n"/>
+      <c r="I13" s="23" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="18" t="inlineStr"/>
-      <c r="B14" s="19" t="inlineStr"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="20">
+      <c r="A14" s="13" t="inlineStr"/>
+      <c r="B14" s="14" t="inlineStr"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="16">
         <f>IF($A14="","",IF(COUNT(E14:F14)=0,"",SUM(E14:F14)))</f>
         <v/>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="17">
         <f>IF($A14="","",IF(SUM(E14:F14)&gt;0,"Sí","No"))</f>
         <v/>
       </c>
-      <c r="I14" s="22" t="n"/>
-    </row>
-    <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="I14" s="18" t="n"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="19" t="inlineStr"/>
+      <c r="B15" s="20" t="inlineStr"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="21">
+        <f>IF($A15="","",IF(COUNT(E15:F15)=0,"",SUM(E15:F15)))</f>
+        <v/>
+      </c>
+      <c r="H15" s="22">
+        <f>IF($A15="","",IF(SUM(E15:F15)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I15" s="23" t="n"/>
+    </row>
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>CARNE MART</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Chiles</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>lata</t>
         </is>
       </c>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15">
-        <f>IF($A16="","",IF(COUNT(E16:F16)=0,"",SUM(E16:F16)))</f>
-        <v/>
-      </c>
-      <c r="H16" s="16">
-        <f>IF($A16="","",IF(SUM(E16:F16)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I16" s="17" t="n"/>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="16">
+        <f>IF($A17="","",IF(COUNT(E17:F17)=0,"",SUM(E17:F17)))</f>
+        <v/>
+      </c>
+      <c r="H17" s="17">
+        <f>IF($A17="","",IF(SUM(E17:F17)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I17" s="18" t="n"/>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Mayonesa</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="20">
-        <f>IF($A17="","",IF(COUNT(E17:F17)=0,"",SUM(E17:F17)))</f>
-        <v/>
-      </c>
-      <c r="H17" s="21">
-        <f>IF($A17="","",IF(SUM(E17:F17)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I17" s="22" t="n"/>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="21">
+        <f>IF($A18="","",IF(COUNT(E18:F18)=0,"",SUM(E18:F18)))</f>
+        <v/>
+      </c>
+      <c r="H18" s="22">
+        <f>IF($A18="","",IF(SUM(E18:F18)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I18" s="23" t="n"/>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Mostaza</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="14" t="n"/>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="15">
-        <f>IF($A18="","",IF(COUNT(E18:F18)=0,"",SUM(E18:F18)))</f>
-        <v/>
-      </c>
-      <c r="H18" s="16">
-        <f>IF($A18="","",IF(SUM(E18:F18)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I18" s="17" t="n"/>
-    </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="16">
+        <f>IF($A19="","",IF(COUNT(E19:F19)=0,"",SUM(E19:F19)))</f>
+        <v/>
+      </c>
+      <c r="H19" s="17">
+        <f>IF($A19="","",IF(SUM(E19:F19)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I19" s="18" t="n"/>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>Manteca</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="14" t="n"/>
-      <c r="E19" s="14" t="n"/>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="20">
-        <f>IF($A19="","",IF(COUNT(E19:F19)=0,"",SUM(E19:F19)))</f>
-        <v/>
-      </c>
-      <c r="H19" s="21">
-        <f>IF($A19="","",IF(SUM(E19:F19)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I19" s="22" t="n"/>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="12" t="inlineStr"/>
-      <c r="B20" s="13" t="inlineStr"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="14" t="n"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15">
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="21">
         <f>IF($A20="","",IF(COUNT(E20:F20)=0,"",SUM(E20:F20)))</f>
         <v/>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="22">
         <f>IF($A20="","",IF(SUM(E20:F20)&gt;0,"Sí","No"))</f>
         <v/>
       </c>
-      <c r="I20" s="17" t="n"/>
+      <c r="I20" s="23" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="18" t="inlineStr"/>
-      <c r="B21" s="19" t="inlineStr"/>
-      <c r="C21" s="14" t="n"/>
-      <c r="D21" s="14" t="n"/>
-      <c r="E21" s="14" t="n"/>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="20">
+      <c r="A21" s="13" t="inlineStr"/>
+      <c r="B21" s="14" t="inlineStr"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="16">
         <f>IF($A21="","",IF(COUNT(E21:F21)=0,"",SUM(E21:F21)))</f>
         <v/>
       </c>
-      <c r="H21" s="21">
+      <c r="H21" s="17">
         <f>IF($A21="","",IF(SUM(E21:F21)&gt;0,"Sí","No"))</f>
         <v/>
       </c>
-      <c r="I21" s="22" t="n"/>
-    </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="I21" s="18" t="n"/>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="19" t="inlineStr"/>
+      <c r="B22" s="20" t="inlineStr"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="21">
+        <f>IF($A22="","",IF(COUNT(E22:F22)=0,"",SUM(E22:F22)))</f>
+        <v/>
+      </c>
+      <c r="H22" s="22">
+        <f>IF($A22="","",IF(SUM(E22:F22)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I22" s="23" t="n"/>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>CÁRNICOS / POA</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
-      <c r="H22" s="11" t="n"/>
-      <c r="I22" s="11" t="n"/>
-    </row>
-    <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Bistec / Adobada</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C23" s="14" t="n"/>
-      <c r="D23" s="14" t="n"/>
-      <c r="E23" s="14" t="n"/>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15">
-        <f>IF($A23="","",IF(COUNT(E23:F23)=0,"",SUM(E23:F23)))</f>
-        <v/>
-      </c>
-      <c r="H23" s="16">
-        <f>IF($A23="","",IF(SUM(E23:F23)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I23" s="17" t="n"/>
-    </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="16">
+        <f>IF($A24="","",IF(COUNT(E24:F24)=0,"",SUM(E24:F24)))</f>
+        <v/>
+      </c>
+      <c r="H24" s="17">
+        <f>IF($A24="","",IF(SUM(E24:F24)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I24" s="18" t="n"/>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Pierna</t>
         </is>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="14" t="n"/>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="20">
-        <f>IF($A24="","",IF(COUNT(E24:F24)=0,"",SUM(E24:F24)))</f>
-        <v/>
-      </c>
-      <c r="H24" s="21">
-        <f>IF($A24="","",IF(SUM(E24:F24)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I24" s="22" t="n"/>
-    </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="21">
+        <f>IF($A25="","",IF(COUNT(E25:F25)=0,"",SUM(E25:F25)))</f>
+        <v/>
+      </c>
+      <c r="H25" s="22">
+        <f>IF($A25="","",IF(SUM(E25:F25)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I25" s="23" t="n"/>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>Chorizo</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="14" t="n"/>
-      <c r="E25" s="14" t="n"/>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="15">
-        <f>IF($A25="","",IF(COUNT(E25:F25)=0,"",SUM(E25:F25)))</f>
-        <v/>
-      </c>
-      <c r="H25" s="16">
-        <f>IF($A25="","",IF(SUM(E25:F25)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I25" s="17" t="n"/>
-    </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="16">
+        <f>IF($A26="","",IF(COUNT(E26:F26)=0,"",SUM(E26:F26)))</f>
+        <v/>
+      </c>
+      <c r="H26" s="17">
+        <f>IF($A26="","",IF(SUM(E26:F26)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I26" s="18" t="n"/>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>Jamón</t>
         </is>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C26" s="14" t="n"/>
-      <c r="D26" s="14" t="n"/>
-      <c r="E26" s="14" t="n"/>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="20">
-        <f>IF($A26="","",IF(COUNT(E26:F26)=0,"",SUM(E26:F26)))</f>
-        <v/>
-      </c>
-      <c r="H26" s="21">
-        <f>IF($A26="","",IF(SUM(E26:F26)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I26" s="22" t="n"/>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="15" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="21">
+        <f>IF($A27="","",IF(COUNT(E27:F27)=0,"",SUM(E27:F27)))</f>
+        <v/>
+      </c>
+      <c r="H27" s="22">
+        <f>IF($A27="","",IF(SUM(E27:F27)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I27" s="23" t="n"/>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>Huevo</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C27" s="14" t="n"/>
-      <c r="D27" s="14" t="n"/>
-      <c r="E27" s="14" t="n"/>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="15">
-        <f>IF($A27="","",IF(COUNT(E27:F27)=0,"",SUM(E27:F27)))</f>
-        <v/>
-      </c>
-      <c r="H27" s="16">
-        <f>IF($A27="","",IF(SUM(E27:F27)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I27" s="17" t="n"/>
-    </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="15" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="16">
+        <f>IF($A28="","",IF(COUNT(E28:F28)=0,"",SUM(E28:F28)))</f>
+        <v/>
+      </c>
+      <c r="H28" s="17">
+        <f>IF($A28="","",IF(SUM(E28:F28)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I28" s="18" t="n"/>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Queso</t>
         </is>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C28" s="14" t="n"/>
-      <c r="D28" s="14" t="n"/>
-      <c r="E28" s="14" t="n"/>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="20">
-        <f>IF($A28="","",IF(COUNT(E28:F28)=0,"",SUM(E28:F28)))</f>
-        <v/>
-      </c>
-      <c r="H28" s="21">
-        <f>IF($A28="","",IF(SUM(E28:F28)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I28" s="22" t="n"/>
-    </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="21">
+        <f>IF($A29="","",IF(COUNT(E29:F29)=0,"",SUM(E29:F29)))</f>
+        <v/>
+      </c>
+      <c r="H29" s="22">
+        <f>IF($A29="","",IF(SUM(E29:F29)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I29" s="23" t="n"/>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>Leche</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>lt</t>
         </is>
       </c>
-      <c r="C29" s="14" t="n"/>
-      <c r="D29" s="14" t="n"/>
-      <c r="E29" s="14" t="n"/>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="15">
-        <f>IF($A29="","",IF(COUNT(E29:F29)=0,"",SUM(E29:F29)))</f>
-        <v/>
-      </c>
-      <c r="H29" s="16">
-        <f>IF($A29="","",IF(SUM(E29:F29)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I29" s="17" t="n"/>
-    </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="18" t="inlineStr"/>
-      <c r="B30" s="19" t="inlineStr"/>
-      <c r="C30" s="14" t="n"/>
-      <c r="D30" s="14" t="n"/>
-      <c r="E30" s="14" t="n"/>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="20">
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="16">
         <f>IF($A30="","",IF(COUNT(E30:F30)=0,"",SUM(E30:F30)))</f>
         <v/>
       </c>
-      <c r="H30" s="21">
+      <c r="H30" s="17">
         <f>IF($A30="","",IF(SUM(E30:F30)&gt;0,"Sí","No"))</f>
         <v/>
       </c>
-      <c r="I30" s="22" t="n"/>
+      <c r="I30" s="18" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="12" t="inlineStr"/>
-      <c r="B31" s="13" t="inlineStr"/>
-      <c r="C31" s="14" t="n"/>
-      <c r="D31" s="14" t="n"/>
-      <c r="E31" s="14" t="n"/>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="15">
+      <c r="A31" s="19" t="inlineStr"/>
+      <c r="B31" s="20" t="inlineStr"/>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="21">
         <f>IF($A31="","",IF(COUNT(E31:F31)=0,"",SUM(E31:F31)))</f>
         <v/>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="22">
         <f>IF($A31="","",IF(SUM(E31:F31)&gt;0,"Sí","No"))</f>
         <v/>
       </c>
-      <c r="I31" s="17" t="n"/>
-    </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="I31" s="23" t="n"/>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="13" t="inlineStr"/>
+      <c r="B32" s="14" t="inlineStr"/>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="16">
+        <f>IF($A32="","",IF(COUNT(E32:F32)=0,"",SUM(E32:F32)))</f>
+        <v/>
+      </c>
+      <c r="H32" s="17">
+        <f>IF($A32="","",IF(SUM(E32:F32)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I32" s="18" t="n"/>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>CONDIMENTOS</t>
         </is>
       </c>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="11" t="n"/>
-      <c r="I32" s="11" t="n"/>
-    </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>Pimienta</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C33" s="14" t="n"/>
-      <c r="D33" s="14" t="n"/>
-      <c r="E33" s="14" t="n"/>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="15">
-        <f>IF($A33="","",IF(COUNT(E33:F33)=0,"",SUM(E33:F33)))</f>
-        <v/>
-      </c>
-      <c r="H33" s="16">
-        <f>IF($A33="","",IF(SUM(E33:F33)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I33" s="17" t="n"/>
-    </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="15" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="16">
+        <f>IF($A34="","",IF(COUNT(E34:F34)=0,"",SUM(E34:F34)))</f>
+        <v/>
+      </c>
+      <c r="H34" s="17">
+        <f>IF($A34="","",IF(SUM(E34:F34)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I34" s="18" t="n"/>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Ajo en polvo</t>
         </is>
       </c>
-      <c r="B34" s="19" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C34" s="14" t="n"/>
-      <c r="D34" s="14" t="n"/>
-      <c r="E34" s="14" t="n"/>
-      <c r="F34" s="14" t="n"/>
-      <c r="G34" s="20">
-        <f>IF($A34="","",IF(COUNT(E34:F34)=0,"",SUM(E34:F34)))</f>
-        <v/>
-      </c>
-      <c r="H34" s="21">
-        <f>IF($A34="","",IF(SUM(E34:F34)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I34" s="22" t="n"/>
-    </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="15" t="n"/>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="21">
+        <f>IF($A35="","",IF(COUNT(E35:F35)=0,"",SUM(E35:F35)))</f>
+        <v/>
+      </c>
+      <c r="H35" s="22">
+        <f>IF($A35="","",IF(SUM(E35:F35)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I35" s="23" t="n"/>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>Sazonador</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C35" s="14" t="n"/>
-      <c r="D35" s="14" t="n"/>
-      <c r="E35" s="14" t="n"/>
-      <c r="F35" s="14" t="n"/>
-      <c r="G35" s="15">
-        <f>IF($A35="","",IF(COUNT(E35:F35)=0,"",SUM(E35:F35)))</f>
-        <v/>
-      </c>
-      <c r="H35" s="16">
-        <f>IF($A35="","",IF(SUM(E35:F35)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I35" s="17" t="n"/>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="15" t="n"/>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="16">
+        <f>IF($A36="","",IF(COUNT(E36:F36)=0,"",SUM(E36:F36)))</f>
+        <v/>
+      </c>
+      <c r="H36" s="17">
+        <f>IF($A36="","",IF(SUM(E36:F36)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I36" s="18" t="n"/>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>Salsa Inglesa</t>
         </is>
       </c>
-      <c r="B36" s="19" t="inlineStr">
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="14" t="n"/>
-      <c r="E36" s="14" t="n"/>
-      <c r="F36" s="14" t="n"/>
-      <c r="G36" s="20">
-        <f>IF($A36="","",IF(COUNT(E36:F36)=0,"",SUM(E36:F36)))</f>
-        <v/>
-      </c>
-      <c r="H36" s="21">
-        <f>IF($A36="","",IF(SUM(E36:F36)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I36" s="22" t="n"/>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="15" t="n"/>
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="15" t="n"/>
+      <c r="G37" s="21">
+        <f>IF($A37="","",IF(COUNT(E37:F37)=0,"",SUM(E37:F37)))</f>
+        <v/>
+      </c>
+      <c r="H37" s="22">
+        <f>IF($A37="","",IF(SUM(E37:F37)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I37" s="23" t="n"/>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>Jugo Maggi</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C37" s="14" t="n"/>
-      <c r="D37" s="14" t="n"/>
-      <c r="E37" s="14" t="n"/>
-      <c r="F37" s="14" t="n"/>
-      <c r="G37" s="15">
-        <f>IF($A37="","",IF(COUNT(E37:F37)=0,"",SUM(E37:F37)))</f>
-        <v/>
-      </c>
-      <c r="H37" s="16">
-        <f>IF($A37="","",IF(SUM(E37:F37)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I37" s="17" t="n"/>
-    </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="16">
+        <f>IF($A38="","",IF(COUNT(E38:F38)=0,"",SUM(E38:F38)))</f>
+        <v/>
+      </c>
+      <c r="H38" s="17">
+        <f>IF($A38="","",IF(SUM(E38:F38)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I38" s="18" t="n"/>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>Aceite</t>
         </is>
       </c>
-      <c r="B38" s="19" t="inlineStr">
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>lt</t>
         </is>
       </c>
-      <c r="C38" s="14" t="n"/>
-      <c r="D38" s="14" t="n"/>
-      <c r="E38" s="14" t="n"/>
-      <c r="F38" s="14" t="n"/>
-      <c r="G38" s="20">
-        <f>IF($A38="","",IF(COUNT(E38:F38)=0,"",SUM(E38:F38)))</f>
-        <v/>
-      </c>
-      <c r="H38" s="21">
-        <f>IF($A38="","",IF(SUM(E38:F38)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I38" s="22" t="n"/>
-    </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="12" t="inlineStr"/>
-      <c r="B39" s="13" t="inlineStr"/>
-      <c r="C39" s="14" t="n"/>
-      <c r="D39" s="14" t="n"/>
-      <c r="E39" s="14" t="n"/>
-      <c r="F39" s="14" t="n"/>
-      <c r="G39" s="15">
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="21">
         <f>IF($A39="","",IF(COUNT(E39:F39)=0,"",SUM(E39:F39)))</f>
         <v/>
       </c>
-      <c r="H39" s="16">
+      <c r="H39" s="22">
         <f>IF($A39="","",IF(SUM(E39:F39)&gt;0,"Sí","No"))</f>
         <v/>
       </c>
-      <c r="I39" s="17" t="n"/>
+      <c r="I39" s="23" t="n"/>
     </row>
     <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="18" t="inlineStr"/>
-      <c r="B40" s="19" t="inlineStr"/>
-      <c r="C40" s="14" t="n"/>
-      <c r="D40" s="14" t="n"/>
-      <c r="E40" s="14" t="n"/>
-      <c r="F40" s="14" t="n"/>
-      <c r="G40" s="20">
+      <c r="A40" s="13" t="inlineStr"/>
+      <c r="B40" s="14" t="inlineStr"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="15" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="16">
         <f>IF($A40="","",IF(COUNT(E40:F40)=0,"",SUM(E40:F40)))</f>
         <v/>
       </c>
-      <c r="H40" s="21">
+      <c r="H40" s="17">
         <f>IF($A40="","",IF(SUM(E40:F40)&gt;0,"Sí","No"))</f>
         <v/>
       </c>
-      <c r="I40" s="22" t="n"/>
-    </row>
-    <row r="41" ht="19" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="I40" s="18" t="n"/>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="19" t="inlineStr"/>
+      <c r="B41" s="20" t="inlineStr"/>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="15" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="15" t="n"/>
+      <c r="G41" s="21">
+        <f>IF($A41="","",IF(COUNT(E41:F41)=0,"",SUM(E41:F41)))</f>
+        <v/>
+      </c>
+      <c r="H41" s="22">
+        <f>IF($A41="","",IF(SUM(E41:F41)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I41" s="23" t="n"/>
+    </row>
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>LIMPIEZA</t>
         </is>
       </c>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="11" t="n"/>
-      <c r="G41" s="11" t="n"/>
-      <c r="H41" s="11" t="n"/>
-      <c r="I41" s="11" t="n"/>
-    </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="12" t="n"/>
+      <c r="G42" s="12" t="n"/>
+      <c r="H42" s="12" t="n"/>
+      <c r="I42" s="12" t="n"/>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>Cloro</t>
         </is>
       </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>lt</t>
         </is>
       </c>
-      <c r="C42" s="14" t="n"/>
-      <c r="D42" s="14" t="n"/>
-      <c r="E42" s="14" t="n"/>
-      <c r="F42" s="14" t="n"/>
-      <c r="G42" s="15">
-        <f>IF($A42="","",IF(COUNT(E42:F42)=0,"",SUM(E42:F42)))</f>
-        <v/>
-      </c>
-      <c r="H42" s="16">
-        <f>IF($A42="","",IF(SUM(E42:F42)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I42" s="17" t="n"/>
-    </row>
-    <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="C43" s="15" t="n"/>
+      <c r="D43" s="15" t="n"/>
+      <c r="E43" s="15" t="n"/>
+      <c r="F43" s="15" t="n"/>
+      <c r="G43" s="16">
+        <f>IF($A43="","",IF(COUNT(E43:F43)=0,"",SUM(E43:F43)))</f>
+        <v/>
+      </c>
+      <c r="H43" s="17">
+        <f>IF($A43="","",IF(SUM(E43:F43)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I43" s="18" t="n"/>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>Fabuloso</t>
         </is>
       </c>
-      <c r="B43" s="19" t="inlineStr">
+      <c r="B44" s="20" t="inlineStr">
         <is>
           <t>lt</t>
         </is>
       </c>
-      <c r="C43" s="14" t="n"/>
-      <c r="D43" s="14" t="n"/>
-      <c r="E43" s="14" t="n"/>
-      <c r="F43" s="14" t="n"/>
-      <c r="G43" s="20">
-        <f>IF($A43="","",IF(COUNT(E43:F43)=0,"",SUM(E43:F43)))</f>
-        <v/>
-      </c>
-      <c r="H43" s="21">
-        <f>IF($A43="","",IF(SUM(E43:F43)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I43" s="22" t="n"/>
-    </row>
-    <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
+      <c r="C44" s="15" t="n"/>
+      <c r="D44" s="15" t="n"/>
+      <c r="E44" s="15" t="n"/>
+      <c r="F44" s="15" t="n"/>
+      <c r="G44" s="21">
+        <f>IF($A44="","",IF(COUNT(E44:F44)=0,"",SUM(E44:F44)))</f>
+        <v/>
+      </c>
+      <c r="H44" s="22">
+        <f>IF($A44="","",IF(SUM(E44:F44)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I44" s="23" t="n"/>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>Desengrasante</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>lt</t>
         </is>
       </c>
-      <c r="C44" s="14" t="n"/>
-      <c r="D44" s="14" t="n"/>
-      <c r="E44" s="14" t="n"/>
-      <c r="F44" s="14" t="n"/>
-      <c r="G44" s="15">
-        <f>IF($A44="","",IF(COUNT(E44:F44)=0,"",SUM(E44:F44)))</f>
-        <v/>
-      </c>
-      <c r="H44" s="16">
-        <f>IF($A44="","",IF(SUM(E44:F44)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I44" s="17" t="n"/>
-    </row>
-    <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="18" t="inlineStr"/>
-      <c r="B45" s="19" t="inlineStr"/>
-      <c r="C45" s="14" t="n"/>
-      <c r="D45" s="14" t="n"/>
-      <c r="E45" s="14" t="n"/>
-      <c r="F45" s="14" t="n"/>
-      <c r="G45" s="20">
+      <c r="C45" s="15" t="n"/>
+      <c r="D45" s="15" t="n"/>
+      <c r="E45" s="15" t="n"/>
+      <c r="F45" s="15" t="n"/>
+      <c r="G45" s="16">
         <f>IF($A45="","",IF(COUNT(E45:F45)=0,"",SUM(E45:F45)))</f>
         <v/>
       </c>
-      <c r="H45" s="21">
+      <c r="H45" s="17">
         <f>IF($A45="","",IF(SUM(E45:F45)&gt;0,"Sí","No"))</f>
         <v/>
       </c>
-      <c r="I45" s="22" t="n"/>
+      <c r="I45" s="18" t="n"/>
     </row>
     <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="12" t="inlineStr"/>
-      <c r="B46" s="13" t="inlineStr"/>
-      <c r="C46" s="14" t="n"/>
-      <c r="D46" s="14" t="n"/>
-      <c r="E46" s="14" t="n"/>
-      <c r="F46" s="14" t="n"/>
-      <c r="G46" s="15">
+      <c r="A46" s="19" t="inlineStr"/>
+      <c r="B46" s="20" t="inlineStr"/>
+      <c r="C46" s="15" t="n"/>
+      <c r="D46" s="15" t="n"/>
+      <c r="E46" s="15" t="n"/>
+      <c r="F46" s="15" t="n"/>
+      <c r="G46" s="21">
         <f>IF($A46="","",IF(COUNT(E46:F46)=0,"",SUM(E46:F46)))</f>
         <v/>
       </c>
-      <c r="H46" s="16">
+      <c r="H46" s="22">
         <f>IF($A46="","",IF(SUM(E46:F46)&gt;0,"Sí","No"))</f>
         <v/>
       </c>
-      <c r="I46" s="17" t="n"/>
-    </row>
-    <row r="47" ht="19" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="I46" s="23" t="n"/>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="13" t="inlineStr"/>
+      <c r="B47" s="14" t="inlineStr"/>
+      <c r="C47" s="15" t="n"/>
+      <c r="D47" s="15" t="n"/>
+      <c r="E47" s="15" t="n"/>
+      <c r="F47" s="15" t="n"/>
+      <c r="G47" s="16">
+        <f>IF($A47="","",IF(COUNT(E47:F47)=0,"",SUM(E47:F47)))</f>
+        <v/>
+      </c>
+      <c r="H47" s="17">
+        <f>IF($A47="","",IF(SUM(E47:F47)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I47" s="18" t="n"/>
+    </row>
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>PAPELERÍA</t>
         </is>
       </c>
-      <c r="B47" s="11" t="n"/>
-      <c r="C47" s="11" t="n"/>
-      <c r="D47" s="11" t="n"/>
-      <c r="E47" s="11" t="n"/>
-      <c r="F47" s="11" t="n"/>
-      <c r="G47" s="11" t="n"/>
-      <c r="H47" s="11" t="n"/>
-      <c r="I47" s="11" t="n"/>
-    </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="B48" s="12" t="n"/>
+      <c r="C48" s="12" t="n"/>
+      <c r="D48" s="12" t="n"/>
+      <c r="E48" s="12" t="n"/>
+      <c r="F48" s="12" t="n"/>
+      <c r="G48" s="12" t="n"/>
+      <c r="H48" s="12" t="n"/>
+      <c r="I48" s="12" t="n"/>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>Servilletas</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>paq</t>
         </is>
       </c>
-      <c r="C48" s="14" t="n"/>
-      <c r="D48" s="14" t="n"/>
-      <c r="E48" s="14" t="n"/>
-      <c r="F48" s="14" t="n"/>
-      <c r="G48" s="15">
-        <f>IF($A48="","",IF(COUNT(E48:F48)=0,"",SUM(E48:F48)))</f>
-        <v/>
-      </c>
-      <c r="H48" s="16">
-        <f>IF($A48="","",IF(SUM(E48:F48)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I48" s="17" t="n"/>
-    </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="18" t="inlineStr">
+      <c r="C49" s="15" t="n"/>
+      <c r="D49" s="15" t="n"/>
+      <c r="E49" s="15" t="n"/>
+      <c r="F49" s="15" t="n"/>
+      <c r="G49" s="16">
+        <f>IF($A49="","",IF(COUNT(E49:F49)=0,"",SUM(E49:F49)))</f>
+        <v/>
+      </c>
+      <c r="H49" s="17">
+        <f>IF($A49="","",IF(SUM(E49:F49)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I49" s="18" t="n"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>Sanitas</t>
         </is>
       </c>
-      <c r="B49" s="19" t="inlineStr">
+      <c r="B50" s="20" t="inlineStr">
         <is>
           <t>paq</t>
         </is>
       </c>
-      <c r="C49" s="14" t="n"/>
-      <c r="D49" s="14" t="n"/>
-      <c r="E49" s="14" t="n"/>
-      <c r="F49" s="14" t="n"/>
-      <c r="G49" s="20">
-        <f>IF($A49="","",IF(COUNT(E49:F49)=0,"",SUM(E49:F49)))</f>
-        <v/>
-      </c>
-      <c r="H49" s="21">
-        <f>IF($A49="","",IF(SUM(E49:F49)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I49" s="22" t="n"/>
-    </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="12" t="inlineStr">
+      <c r="C50" s="15" t="n"/>
+      <c r="D50" s="15" t="n"/>
+      <c r="E50" s="15" t="n"/>
+      <c r="F50" s="15" t="n"/>
+      <c r="G50" s="21">
+        <f>IF($A50="","",IF(COUNT(E50:F50)=0,"",SUM(E50:F50)))</f>
+        <v/>
+      </c>
+      <c r="H50" s="22">
+        <f>IF($A50="","",IF(SUM(E50:F50)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I50" s="23" t="n"/>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>Aluminio</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>rollo</t>
         </is>
       </c>
-      <c r="C50" s="14" t="n"/>
-      <c r="D50" s="14" t="n"/>
-      <c r="E50" s="14" t="n"/>
-      <c r="F50" s="14" t="n"/>
-      <c r="G50" s="15">
-        <f>IF($A50="","",IF(COUNT(E50:F50)=0,"",SUM(E50:F50)))</f>
-        <v/>
-      </c>
-      <c r="H50" s="16">
-        <f>IF($A50="","",IF(SUM(E50:F50)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I50" s="17" t="n"/>
-    </row>
-    <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="C51" s="15" t="n"/>
+      <c r="D51" s="15" t="n"/>
+      <c r="E51" s="15" t="n"/>
+      <c r="F51" s="15" t="n"/>
+      <c r="G51" s="16">
+        <f>IF($A51="","",IF(COUNT(E51:F51)=0,"",SUM(E51:F51)))</f>
+        <v/>
+      </c>
+      <c r="H51" s="17">
+        <f>IF($A51="","",IF(SUM(E51:F51)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I51" s="18" t="n"/>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>Papel de baño</t>
         </is>
       </c>
-      <c r="B51" s="19" t="inlineStr">
+      <c r="B52" s="20" t="inlineStr">
         <is>
           <t>paq</t>
         </is>
       </c>
-      <c r="C51" s="14" t="n"/>
-      <c r="D51" s="14" t="n"/>
-      <c r="E51" s="14" t="n"/>
-      <c r="F51" s="14" t="n"/>
-      <c r="G51" s="20">
-        <f>IF($A51="","",IF(COUNT(E51:F51)=0,"",SUM(E51:F51)))</f>
-        <v/>
-      </c>
-      <c r="H51" s="21">
-        <f>IF($A51="","",IF(SUM(E51:F51)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I51" s="22" t="n"/>
-    </row>
-    <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="12" t="inlineStr">
+      <c r="C52" s="15" t="n"/>
+      <c r="D52" s="15" t="n"/>
+      <c r="E52" s="15" t="n"/>
+      <c r="F52" s="15" t="n"/>
+      <c r="G52" s="21">
+        <f>IF($A52="","",IF(COUNT(E52:F52)=0,"",SUM(E52:F52)))</f>
+        <v/>
+      </c>
+      <c r="H52" s="22">
+        <f>IF($A52="","",IF(SUM(E52:F52)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I52" s="23" t="n"/>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>Servitoalla</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>paq</t>
         </is>
       </c>
-      <c r="C52" s="14" t="n"/>
-      <c r="D52" s="14" t="n"/>
-      <c r="E52" s="14" t="n"/>
-      <c r="F52" s="14" t="n"/>
-      <c r="G52" s="15">
-        <f>IF($A52="","",IF(COUNT(E52:F52)=0,"",SUM(E52:F52)))</f>
-        <v/>
-      </c>
-      <c r="H52" s="16">
-        <f>IF($A52="","",IF(SUM(E52:F52)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I52" s="17" t="n"/>
-    </row>
-    <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="18" t="inlineStr"/>
-      <c r="B53" s="19" t="inlineStr"/>
-      <c r="C53" s="14" t="n"/>
-      <c r="D53" s="14" t="n"/>
-      <c r="E53" s="14" t="n"/>
-      <c r="F53" s="14" t="n"/>
-      <c r="G53" s="20">
+      <c r="C53" s="15" t="n"/>
+      <c r="D53" s="15" t="n"/>
+      <c r="E53" s="15" t="n"/>
+      <c r="F53" s="15" t="n"/>
+      <c r="G53" s="16">
         <f>IF($A53="","",IF(COUNT(E53:F53)=0,"",SUM(E53:F53)))</f>
         <v/>
       </c>
-      <c r="H53" s="21">
+      <c r="H53" s="17">
         <f>IF($A53="","",IF(SUM(E53:F53)&gt;0,"Sí","No"))</f>
         <v/>
       </c>
-      <c r="I53" s="22" t="n"/>
+      <c r="I53" s="18" t="n"/>
     </row>
     <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="12" t="inlineStr"/>
-      <c r="B54" s="13" t="inlineStr"/>
-      <c r="C54" s="14" t="n"/>
-      <c r="D54" s="14" t="n"/>
-      <c r="E54" s="14" t="n"/>
-      <c r="F54" s="14" t="n"/>
-      <c r="G54" s="15">
+      <c r="A54" s="19" t="inlineStr"/>
+      <c r="B54" s="20" t="inlineStr"/>
+      <c r="C54" s="15" t="n"/>
+      <c r="D54" s="15" t="n"/>
+      <c r="E54" s="15" t="n"/>
+      <c r="F54" s="15" t="n"/>
+      <c r="G54" s="21">
         <f>IF($A54="","",IF(COUNT(E54:F54)=0,"",SUM(E54:F54)))</f>
         <v/>
       </c>
-      <c r="H54" s="16">
+      <c r="H54" s="22">
         <f>IF($A54="","",IF(SUM(E54:F54)&gt;0,"Sí","No"))</f>
         <v/>
       </c>
-      <c r="I54" s="17" t="n"/>
-    </row>
-    <row r="55" ht="19" customHeight="1">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="I54" s="23" t="n"/>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="13" t="inlineStr"/>
+      <c r="B55" s="14" t="inlineStr"/>
+      <c r="C55" s="15" t="n"/>
+      <c r="D55" s="15" t="n"/>
+      <c r="E55" s="15" t="n"/>
+      <c r="F55" s="15" t="n"/>
+      <c r="G55" s="16">
+        <f>IF($A55="","",IF(COUNT(E55:F55)=0,"",SUM(E55:F55)))</f>
+        <v/>
+      </c>
+      <c r="H55" s="17">
+        <f>IF($A55="","",IF(SUM(E55:F55)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I55" s="18" t="n"/>
+    </row>
+    <row r="56" ht="19" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>OTROS</t>
         </is>
       </c>
-      <c r="B55" s="11" t="n"/>
-      <c r="C55" s="11" t="n"/>
-      <c r="D55" s="11" t="n"/>
-      <c r="E55" s="11" t="n"/>
-      <c r="F55" s="11" t="n"/>
-      <c r="G55" s="11" t="n"/>
-      <c r="H55" s="11" t="n"/>
-      <c r="I55" s="11" t="n"/>
-    </row>
-    <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="12" t="inlineStr">
+      <c r="B56" s="12" t="n"/>
+      <c r="C56" s="12" t="n"/>
+      <c r="D56" s="12" t="n"/>
+      <c r="E56" s="12" t="n"/>
+      <c r="F56" s="12" t="n"/>
+      <c r="G56" s="12" t="n"/>
+      <c r="H56" s="12" t="n"/>
+      <c r="I56" s="12" t="n"/>
+    </row>
+    <row r="57" ht="17" customHeight="1">
+      <c r="A57" s="13" t="inlineStr">
         <is>
           <t>Tortillas</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="C56" s="14" t="n"/>
-      <c r="D56" s="14" t="n"/>
-      <c r="E56" s="14" t="n"/>
-      <c r="F56" s="14" t="n"/>
-      <c r="G56" s="15">
-        <f>IF($A56="","",IF(COUNT(E56:F56)=0,"",SUM(E56:F56)))</f>
-        <v/>
-      </c>
-      <c r="H56" s="16">
-        <f>IF($A56="","",IF(SUM(E56:F56)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I56" s="17" t="n"/>
-    </row>
-    <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="18" t="inlineStr">
+      <c r="C57" s="15" t="n"/>
+      <c r="D57" s="15" t="n"/>
+      <c r="E57" s="15" t="n"/>
+      <c r="F57" s="15" t="n"/>
+      <c r="G57" s="16">
+        <f>IF($A57="","",IF(COUNT(E57:F57)=0,"",SUM(E57:F57)))</f>
+        <v/>
+      </c>
+      <c r="H57" s="17">
+        <f>IF($A57="","",IF(SUM(E57:F57)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I57" s="18" t="n"/>
+    </row>
+    <row r="58" ht="17" customHeight="1">
+      <c r="A58" s="19" t="inlineStr">
         <is>
           <t>Porcionadoras</t>
         </is>
       </c>
-      <c r="B57" s="19" t="inlineStr">
+      <c r="B58" s="20" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C57" s="14" t="n"/>
-      <c r="D57" s="14" t="n"/>
-      <c r="E57" s="14" t="n"/>
-      <c r="F57" s="14" t="n"/>
-      <c r="G57" s="20">
-        <f>IF($A57="","",IF(COUNT(E57:F57)=0,"",SUM(E57:F57)))</f>
-        <v/>
-      </c>
-      <c r="H57" s="21">
-        <f>IF($A57="","",IF(SUM(E57:F57)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I57" s="22" t="n"/>
-    </row>
-    <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="C58" s="15" t="n"/>
+      <c r="D58" s="15" t="n"/>
+      <c r="E58" s="15" t="n"/>
+      <c r="F58" s="15" t="n"/>
+      <c r="G58" s="21">
+        <f>IF($A58="","",IF(COUNT(E58:F58)=0,"",SUM(E58:F58)))</f>
+        <v/>
+      </c>
+      <c r="H58" s="22">
+        <f>IF($A58="","",IF(SUM(E58:F58)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I58" s="23" t="n"/>
+    </row>
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>Bolsas para basura</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>paq</t>
         </is>
       </c>
-      <c r="C58" s="14" t="n"/>
-      <c r="D58" s="14" t="n"/>
-      <c r="E58" s="14" t="n"/>
-      <c r="F58" s="14" t="n"/>
-      <c r="G58" s="15">
-        <f>IF($A58="","",IF(COUNT(E58:F58)=0,"",SUM(E58:F58)))</f>
-        <v/>
-      </c>
-      <c r="H58" s="16">
-        <f>IF($A58="","",IF(SUM(E58:F58)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I58" s="17" t="n"/>
-    </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="18" t="inlineStr">
+      <c r="C59" s="15" t="n"/>
+      <c r="D59" s="15" t="n"/>
+      <c r="E59" s="15" t="n"/>
+      <c r="F59" s="15" t="n"/>
+      <c r="G59" s="16">
+        <f>IF($A59="","",IF(COUNT(E59:F59)=0,"",SUM(E59:F59)))</f>
+        <v/>
+      </c>
+      <c r="H59" s="17">
+        <f>IF($A59="","",IF(SUM(E59:F59)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I59" s="18" t="n"/>
+    </row>
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="19" t="inlineStr">
         <is>
           <t>Microdyn</t>
         </is>
       </c>
-      <c r="B59" s="19" t="inlineStr">
+      <c r="B60" s="20" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C59" s="14" t="n"/>
-      <c r="D59" s="14" t="n"/>
-      <c r="E59" s="14" t="n"/>
-      <c r="F59" s="14" t="n"/>
-      <c r="G59" s="20">
-        <f>IF($A59="","",IF(COUNT(E59:F59)=0,"",SUM(E59:F59)))</f>
-        <v/>
-      </c>
-      <c r="H59" s="21">
-        <f>IF($A59="","",IF(SUM(E59:F59)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I59" s="22" t="n"/>
-    </row>
-    <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="12" t="inlineStr">
+      <c r="C60" s="15" t="n"/>
+      <c r="D60" s="15" t="n"/>
+      <c r="E60" s="15" t="n"/>
+      <c r="F60" s="15" t="n"/>
+      <c r="G60" s="21">
+        <f>IF($A60="","",IF(COUNT(E60:F60)=0,"",SUM(E60:F60)))</f>
+        <v/>
+      </c>
+      <c r="H60" s="22">
+        <f>IF($A60="","",IF(SUM(E60:F60)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I60" s="23" t="n"/>
+    </row>
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="13" t="inlineStr">
         <is>
           <t>Malteada chocolate</t>
         </is>
       </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C60" s="14" t="n"/>
-      <c r="D60" s="14" t="n"/>
-      <c r="E60" s="14" t="n"/>
-      <c r="F60" s="14" t="n"/>
-      <c r="G60" s="15">
-        <f>IF($A60="","",IF(COUNT(E60:F60)=0,"",SUM(E60:F60)))</f>
-        <v/>
-      </c>
-      <c r="H60" s="16">
-        <f>IF($A60="","",IF(SUM(E60:F60)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I60" s="17" t="n"/>
-    </row>
-    <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="18" t="inlineStr">
+      <c r="C61" s="15" t="n"/>
+      <c r="D61" s="15" t="n"/>
+      <c r="E61" s="15" t="n"/>
+      <c r="F61" s="15" t="n"/>
+      <c r="G61" s="16">
+        <f>IF($A61="","",IF(COUNT(E61:F61)=0,"",SUM(E61:F61)))</f>
+        <v/>
+      </c>
+      <c r="H61" s="17">
+        <f>IF($A61="","",IF(SUM(E61:F61)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I61" s="18" t="n"/>
+    </row>
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>Malteada fresa</t>
         </is>
       </c>
-      <c r="B61" s="19" t="inlineStr">
+      <c r="B62" s="20" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C61" s="14" t="n"/>
-      <c r="D61" s="14" t="n"/>
-      <c r="E61" s="14" t="n"/>
-      <c r="F61" s="14" t="n"/>
-      <c r="G61" s="20">
-        <f>IF($A61="","",IF(COUNT(E61:F61)=0,"",SUM(E61:F61)))</f>
-        <v/>
-      </c>
-      <c r="H61" s="21">
-        <f>IF($A61="","",IF(SUM(E61:F61)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I61" s="22" t="n"/>
-    </row>
-    <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="C62" s="15" t="n"/>
+      <c r="D62" s="15" t="n"/>
+      <c r="E62" s="15" t="n"/>
+      <c r="F62" s="15" t="n"/>
+      <c r="G62" s="21">
+        <f>IF($A62="","",IF(COUNT(E62:F62)=0,"",SUM(E62:F62)))</f>
+        <v/>
+      </c>
+      <c r="H62" s="22">
+        <f>IF($A62="","",IF(SUM(E62:F62)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I62" s="23" t="n"/>
+    </row>
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="13" t="inlineStr">
         <is>
           <t>Malteada vainilla</t>
         </is>
       </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>pza</t>
         </is>
       </c>
-      <c r="C62" s="14" t="n"/>
-      <c r="D62" s="14" t="n"/>
-      <c r="E62" s="14" t="n"/>
-      <c r="F62" s="14" t="n"/>
-      <c r="G62" s="15">
-        <f>IF($A62="","",IF(COUNT(E62:F62)=0,"",SUM(E62:F62)))</f>
-        <v/>
-      </c>
-      <c r="H62" s="16">
-        <f>IF($A62="","",IF(SUM(E62:F62)&gt;0,"Sí","No"))</f>
-        <v/>
-      </c>
-      <c r="I62" s="17" t="n"/>
-    </row>
-    <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="18" t="inlineStr"/>
-      <c r="B63" s="19" t="inlineStr"/>
-      <c r="C63" s="14" t="n"/>
-      <c r="D63" s="14" t="n"/>
-      <c r="E63" s="14" t="n"/>
-      <c r="F63" s="14" t="n"/>
-      <c r="G63" s="20">
+      <c r="C63" s="15" t="n"/>
+      <c r="D63" s="15" t="n"/>
+      <c r="E63" s="15" t="n"/>
+      <c r="F63" s="15" t="n"/>
+      <c r="G63" s="16">
         <f>IF($A63="","",IF(COUNT(E63:F63)=0,"",SUM(E63:F63)))</f>
         <v/>
       </c>
-      <c r="H63" s="21">
+      <c r="H63" s="17">
         <f>IF($A63="","",IF(SUM(E63:F63)&gt;0,"Sí","No"))</f>
         <v/>
       </c>
-      <c r="I63" s="22" t="n"/>
+      <c r="I63" s="18" t="n"/>
     </row>
     <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="12" t="inlineStr"/>
-      <c r="B64" s="13" t="inlineStr"/>
-      <c r="C64" s="14" t="n"/>
-      <c r="D64" s="14" t="n"/>
-      <c r="E64" s="14" t="n"/>
-      <c r="F64" s="14" t="n"/>
-      <c r="G64" s="15">
+      <c r="A64" s="19" t="inlineStr"/>
+      <c r="B64" s="20" t="inlineStr"/>
+      <c r="C64" s="15" t="n"/>
+      <c r="D64" s="15" t="n"/>
+      <c r="E64" s="15" t="n"/>
+      <c r="F64" s="15" t="n"/>
+      <c r="G64" s="21">
         <f>IF($A64="","",IF(COUNT(E64:F64)=0,"",SUM(E64:F64)))</f>
         <v/>
       </c>
-      <c r="H64" s="16">
+      <c r="H64" s="22">
         <f>IF($A64="","",IF(SUM(E64:F64)&gt;0,"Sí","No"))</f>
         <v/>
       </c>
-      <c r="I64" s="17" t="n"/>
+      <c r="I64" s="23" t="n"/>
+    </row>
+    <row r="65" ht="17" customHeight="1">
+      <c r="A65" s="13" t="inlineStr"/>
+      <c r="B65" s="14" t="inlineStr"/>
+      <c r="C65" s="15" t="n"/>
+      <c r="D65" s="15" t="n"/>
+      <c r="E65" s="15" t="n"/>
+      <c r="F65" s="15" t="n"/>
+      <c r="G65" s="16">
+        <f>IF($A65="","",IF(COUNT(E65:F65)=0,"",SUM(E65:F65)))</f>
+        <v/>
+      </c>
+      <c r="H65" s="17">
+        <f>IF($A65="","",IF(SUM(E65:F65)&gt;0,"Sí","No"))</f>
+        <v/>
+      </c>
+      <c r="I65" s="18" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A55:I55"/>
+  <mergeCells count="21">
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="I7:I8"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A47:I47"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A16:I16"/>
   </mergeCells>
-  <conditionalFormatting sqref="H8:H64">
+  <conditionalFormatting sqref="H9:H65">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$H8="Sí"</formula>
+      <formula>$H9="Sí"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>$H8="No"</formula>
+      <formula>$H9="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>